--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486892_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486892_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6992</v>
+        <v>2.3762</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6362</v>
+        <v>1.0168</v>
       </c>
       <c r="F2" t="n">
-        <v>1.063</v>
+        <v>1.3594</v>
       </c>
       <c r="G2" t="n">
         <v>1.2042</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>1.1371</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3747</v>
+        <v>0.7553</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0854</v>
+        <v>0.3818</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.507</v>
+        <v>2.2796</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3932</v>
+        <v>1.1066</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1137</v>
+        <v>1.173</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2299</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5315</v>
+        <v>0.3042</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0114</v>
+        <v>-0.2753</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5201</v>
+        <v>0.5794</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.501</v>
+        <v>1.515</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7092</v>
+        <v>1.6046</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2081</v>
+        <v>-0.0896</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4372</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6097</v>
+        <v>0.6237</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4144</v>
+        <v>0.3097</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1953</v>
+        <v>0.3139</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1088</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2008</v>
+        <v>1.1851</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5965</v>
+        <v>1.6696</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3956</v>
+        <v>-0.4846</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0658</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2878</v>
+        <v>0.6964</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9804</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6925</v>
+        <v>0.6036</v>
       </c>
       <c r="V5" t="n">
         <v>0.3491</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9847</v>
+        <v>-0.6503</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8315</v>
+        <v>-2.5564</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8468</v>
+        <v>1.9061</v>
       </c>
       <c r="G6" t="n">
         <v>0.1537</v>
@@ -922,13 +922,13 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4875</v>
+        <v>-0.1531</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6782</v>
+        <v>-0.4032</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1908</v>
+        <v>0.2501</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3944</v>
+        <v>-1.4792</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0701</v>
+        <v>-3.2684</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4645</v>
+        <v>1.7892</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3163</v>
+        <v>-1.7474</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9504</v>
+        <v>-1.129</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3659</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9192</v>
+        <v>-1.9742</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0775</v>
+        <v>-0.6584</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1582</v>
+        <v>-1.3158</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2355</v>
+        <v>0.2268</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0279</v>
+        <v>-0.4706</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2077</v>
+        <v>0.6974</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1006</v>
+        <v>0.0629</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1776</v>
+        <v>-0.2674</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.077</v>
+        <v>0.3304</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9914</v>
+        <v>-1.6596</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3655</v>
+        <v>-0.0633</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6259</v>
+        <v>-1.5962</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0507</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4536</v>
+        <v>0.7855</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.039</v>
+        <v>0.2632</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4927</v>
+        <v>0.5223</v>
       </c>
       <c r="V8" t="n">
         <v>1.6591</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0384</v>
+        <v>-1.9652</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8572</v>
+        <v>0.4696</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8188</v>
+        <v>-2.4348</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7474</v>
+        <v>-1.3163</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.129</v>
+        <v>-0.9504</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.3659</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9742</v>
+        <v>0.9192</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6584</v>
+        <v>1.0775</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3158</v>
+        <v>-0.1582</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2268</v>
+        <v>-2.2355</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4706</v>
+        <v>-2.0279</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6974</v>
+        <v>-0.2077</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4963</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8563</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.36</v>
+        <v>-0.0474</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4556</v>
+        <v>-4.463</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2749</v>
+        <v>-1.9267</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1806</v>
+        <v>-2.5363</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6943</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1504</v>
+        <v>1.1429</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9726</v>
+        <v>0.3756</v>
       </c>
       <c r="U10" t="n">
-        <v>1.123</v>
+        <v>0.7673</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7622</v>
+        <v>-5.5398</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7717</v>
+        <v>-5.4307</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0095</v>
+        <v>-0.1091</v>
       </c>
       <c r="G11" t="n">
         <v>-5.7335</v>
@@ -1312,13 +1312,13 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0636</v>
+        <v>0.1588</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4147</v>
+        <v>-0.0738</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3512</v>
+        <v>0.2326</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.7187</v>
+        <v>-8.401200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.695600000000001</v>
+        <v>-7.378299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0229</v>
+        <v>-1.022900000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-15.9172</v>
@@ -1363,7 +1363,7 @@
         <v>-1.172400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.5205</v>
+        <v>-6.520499999999999</v>
       </c>
       <c r="K12" t="n">
         <v>-4.635600000000001</v>
@@ -1390,10 +1390,10 @@
         <v>11.2939</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9706</v>
+        <v>5.2881</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03689999999999988</v>
+        <v>1.354</v>
       </c>
       <c r="U12" t="n">
         <v>3.934</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1999</v>
+        <v>3.4572</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8728</v>
+        <v>2.9314</v>
       </c>
       <c r="F13" t="n">
-        <v>0.327</v>
+        <v>0.5258</v>
       </c>
       <c r="G13" t="n">
         <v>3.2408</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2289</v>
+        <v>0.4862</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1117</v>
+        <v>0.1703</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1172</v>
+        <v>0.3159</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2965</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9468</v>
+        <v>3.0419</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7845</v>
+        <v>2.9477</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1622</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>2.7129</v>
@@ -1546,13 +1546,13 @@
         <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6207</v>
+        <v>0.7158</v>
       </c>
       <c r="T14" t="n">
-        <v>0.98</v>
+        <v>0.1431</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6407</v>
+        <v>0.5727</v>
       </c>
       <c r="V14" t="n">
         <v>-2.2349</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7226</v>
+        <v>1.9118</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0035</v>
+        <v>1.6962</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7191</v>
+        <v>0.2156</v>
       </c>
       <c r="G15" t="n">
-        <v>3.043</v>
+        <v>3.4901</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3614</v>
+        <v>3.3188</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6816</v>
+        <v>0.1713</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5052</v>
+        <v>2.0288</v>
       </c>
       <c r="K15" t="n">
-        <v>1.966</v>
+        <v>2.6736</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5391</v>
+        <v>-0.6449</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.4613</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3953</v>
+        <v>0.6452</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1425</v>
+        <v>0.8161</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4641</v>
+        <v>0.4107</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5154</v>
+        <v>-0.6925</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.054</v>
+        <v>-0.4845</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5385</v>
+        <v>-0.208</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6591</v>
+        <v>-1.2965</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8377</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>-2.4751</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0767</v>
+        <v>1.4487</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0686</v>
+        <v>1.2127</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0081</v>
+        <v>0.2361</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4901</v>
+        <v>3.043</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3188</v>
+        <v>2.3614</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1713</v>
+        <v>0.6816</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0288</v>
+        <v>2.5052</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6736</v>
+        <v>1.966</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6449</v>
+        <v>0.5391</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4613</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6452</v>
+        <v>0.3953</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8161</v>
+        <v>0.1425</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-3.2855</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5276</v>
+        <v>-0.7893</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1121</v>
+        <v>-0.8447</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4155</v>
+        <v>0.0555</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2965</v>
+        <v>1.6591</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>2.8377</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4751</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7575</v>
+        <v>0.9807</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2862</v>
+        <v>-1.9087</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0437</v>
+        <v>2.8894</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3739</v>
+        <v>3.5072</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2659</v>
+        <v>1.3626</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.108</v>
+        <v>2.1446</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6666</v>
+        <v>2.5509</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3241</v>
+        <v>0.8278</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3425</v>
+        <v>1.7231</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2927</v>
+        <v>0.9563</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0582</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2345</v>
+        <v>0.4215</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8214</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2053</v>
+        <v>-3.2855</v>
       </c>
       <c r="R17" t="n">
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6283</v>
+        <v>-1.4238</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5928</v>
+        <v>-1.1741</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0355</v>
+        <v>-0.2497</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9384</v>
+        <v>1.1561</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>1.1561</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3003</v>
+        <v>0.8028</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4464</v>
+        <v>-0.1816</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.146</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2155</v>
+        <v>-0.3739</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1523</v>
+        <v>-0.2659</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.108</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0784</v>
+        <v>-0.6666</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0389</v>
+        <v>-0.3241</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>-0.3425</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1371</v>
+        <v>0.2927</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1134</v>
+        <v>0.0582</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0238</v>
+        <v>0.2345</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3251</v>
+        <v>-0.583</v>
       </c>
       <c r="T18" t="n">
-        <v>0.368</v>
+        <v>-0.4882</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0429</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>0.9384</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2402</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1961</v>
+        <v>0.2962</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1179</v>
+        <v>-2.9674</v>
       </c>
       <c r="F19" t="n">
-        <v>2.314</v>
+        <v>3.2636</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5072</v>
+        <v>1.1392</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3626</v>
+        <v>1.4047</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1446</v>
+        <v>-0.2655</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5509</v>
+        <v>0.0037</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8278</v>
+        <v>0.2278</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7231</v>
+        <v>-0.2241</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9563</v>
+        <v>1.1355</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5348000000000001</v>
+        <v>1.177</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4215</v>
+        <v>-0.0414</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2588</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.2855</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2083</v>
+        <v>-0.6101</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3833</v>
+        <v>-0.8643</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.825</v>
+        <v>0.2541</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1561</v>
+        <v>1.4098</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>1.1561</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3698</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1766</v>
+        <v>0.028</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8068</v>
+        <v>-0.0362</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1392</v>
+        <v>0.2155</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4047</v>
+        <v>0.1523</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2655</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0037</v>
+        <v>0.0784</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2278</v>
+        <v>0.0389</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2241</v>
+        <v>0.0395</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1355</v>
+        <v>0.1371</v>
       </c>
       <c r="N20" t="n">
-        <v>1.177</v>
+        <v>0.1134</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0414</v>
+        <v>0.0238</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6427</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2761</v>
+        <v>0.0165</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0735</v>
+        <v>-0.0504</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2027</v>
+        <v>0.0669</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4098</v>
+        <v>-0.2402</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2312</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1114</v>
+        <v>-0.8177</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5722</v>
+        <v>-2.7354</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4608</v>
+        <v>1.9176</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0575</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9895</v>
+        <v>0.3042</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.178</v>
+        <v>-0.3411</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1885</v>
+        <v>0.6453</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2965</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>9.718700000000002</v>
+        <v>11.1134</v>
       </c>
       <c r="E22" t="n">
-        <v>1.022899999999998</v>
+        <v>1.0229</v>
       </c>
       <c r="F22" t="n">
-        <v>8.6957</v>
+        <v>10.0905</v>
       </c>
       <c r="G22" t="n">
         <v>15.9173</v>
@@ -2170,13 +2170,13 @@
         <v>10.2671</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.9705</v>
+        <v>-2.576000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.934</v>
+        <v>-3.9339</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.03669999999999984</v>
+        <v>1.358</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2012</v>
